--- a/AAII_Financials/Quarterly/TSCO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TSCO_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>TSCO</t>
   </si>
@@ -656,541 +656,554 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E7" s="2">
         <v>46109</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46018</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45654</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45290</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44828</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44737</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44464</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44282</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44191</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4541300</v>
+      </c>
+      <c r="E8" s="3">
         <v>3592000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3898300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3719000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4439700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3467000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3773500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3468200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4246600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3394800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3659800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3412000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4184700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3299200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4006400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3270800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3903400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3024100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3319300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3017900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3601600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2792300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2878300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2606600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3176300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1959200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2191800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1984100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2353800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1822200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2133300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1881600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2213200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1682900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1952800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1721700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2017800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1564100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1916500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1542700</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2852800</v>
+      </c>
+      <c r="E9" s="3">
         <v>2290900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2528400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2329800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2799800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2211500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2443900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2177800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2691000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2174000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2366800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2161500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2669900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2129300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2642800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2105000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2517200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1967600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2198700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1932600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2314100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1808600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1882700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1658600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2019500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1297900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1450000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1289900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1533000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1207200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1416900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1228500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1443800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1119300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1284200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1121200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1313100</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1045900</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1270300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1007400</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1688500</v>
+      </c>
+      <c r="E10" s="3">
         <v>1301200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1369900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1389200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1640000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1255400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1329600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1290400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1555600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1220900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1293100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1250500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1514800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1169900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1363700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1165800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1386200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1056500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1120600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1085300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1287500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>983700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>995600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>948000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1156800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>661300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>741800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>694200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>820800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>615000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>716400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>653100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>769400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>563600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>668600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>600500</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>704700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>518200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>646200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>535300</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1233,8 +1246,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1355,8 +1369,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1477,13 +1494,16 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>81200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1512,32 +1532,32 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-11300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1545,12 +1565,12 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>69000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1566,8 +1586,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1599,130 +1619,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E15" s="3">
         <v>126600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>127800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>124100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>122100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>120100</v>
       </c>
       <c r="I15" s="3">
         <v>120100</v>
       </c>
       <c r="J15" s="3">
+        <v>120100</v>
+      </c>
+      <c r="K15" s="3">
         <v>113600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>109300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>104300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>103300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>101600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>102300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>97200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>94800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>87200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>83400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>77600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>75400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>69800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>64900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>60100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>58500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>54700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>52500</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>51400</v>
       </c>
       <c r="AC15" s="3">
         <v>51400</v>
       </c>
       <c r="AD15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="AE15" s="3">
         <v>49800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>49000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>45800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>46000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>45000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>43600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>42800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>43100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>41900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>41000</v>
-      </c>
-      <c r="AN15" s="3">
-        <v>39700</v>
       </c>
       <c r="AO15" s="3">
         <v>39700</v>
       </c>
       <c r="AP15" s="3">
+        <v>39700</v>
+      </c>
+      <c r="AQ15" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1762,252 +1788,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3993000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3358600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3600600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3376300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3861900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3217800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3455200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3143600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3685200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3131700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3325600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3082400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3625400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3054800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3647200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2964400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3378400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2779800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3026200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2720700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3115700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2561800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2693800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2354400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2728600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1846700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2001300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1822300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2066200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1718800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1952900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1728500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1939800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1588200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1769000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1573500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1759800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1467700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1721900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1400700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>548300</v>
+      </c>
+      <c r="E18" s="3">
         <v>233400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>297700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>342700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>577800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>249100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>318300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>324600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>561500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>263100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>334200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>329600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>559300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>244400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>359200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>306400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>525000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>244300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>293100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>297200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>485900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>230500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>184500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>252200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>447700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>112600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>190500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>161800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>287600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>103400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>180400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>153100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>273400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>94700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>183800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>148200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>258000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>96400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>194600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>142000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2050,8 +2083,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2094,8 +2128,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2149,11 +2183,11 @@
         <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>100</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
@@ -2172,496 +2206,511 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>679200</v>
+      </c>
+      <c r="E21" s="3">
         <v>360000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>425500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>466800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>699900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>369200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>438400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>438100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>670700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>367400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>437500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>431200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>661600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>341700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>454000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>393600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>608400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>321900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>368500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>367000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>550700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>290600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>243000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>306800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>500300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>164000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>241800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>211600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>336600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>149200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>226300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>198200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>317100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>137600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>227000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>190200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>299000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>136100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>234300</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>177700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E22" s="3">
         <v>19100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11600</v>
-      </c>
-      <c r="L22" s="3">
-        <v>11900</v>
       </c>
       <c r="M22" s="3">
         <v>11900</v>
       </c>
       <c r="N22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="O22" s="3">
         <v>9500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6200</v>
-      </c>
-      <c r="S22" s="3">
-        <v>7100</v>
       </c>
       <c r="T22" s="3">
         <v>7100</v>
       </c>
       <c r="U22" s="3">
+        <v>7100</v>
+      </c>
+      <c r="V22" s="3">
         <v>6500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>6100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>6700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>7200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>8100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>4900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>4500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>4200</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>3800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>3100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>2800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>1700</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>450000</v>
+      </c>
+      <c r="E23" s="3">
         <v>214300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>280900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>328000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>559800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>229500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>301100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>310700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>549800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>251200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>322300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>331400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>547000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>231800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>349000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>300200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>517900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>237200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>286500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>291100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>479200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>223300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>176400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>245000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>439300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>107500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>185600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>156900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>282400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>98500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>175900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>148700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>268500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>90300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>179600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>144500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>254800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>93600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>193000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>140900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>89300</v>
+      </c>
+      <c r="E24" s="3">
         <v>49800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>53500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>68800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>129800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>50100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>64700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>69300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>124700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>53100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>74400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>76400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>125800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>48700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>78100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>66000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>121500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>65200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>66700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>109200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>40500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>54400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>23700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>41400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>34800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>63200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>21600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>39100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>31900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>61200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>18800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>65000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>52600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>94200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>33300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>69400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2782,252 +2831,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>360700</v>
+      </c>
+      <c r="E26" s="3">
         <v>164500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>227400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>259300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>430000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>179400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>236400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>241500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>425200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>198200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>247900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>255000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>421200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>183100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>270900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>234100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>396500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>187200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>221300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>224400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>370000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>181400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>135900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>190600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>338700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>83800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>144200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>122100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>219200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>76800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>136900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>116800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>207300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>71400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>114600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>91900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>160600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>60300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>123600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>89400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>360700</v>
+      </c>
+      <c r="E27" s="3">
         <v>164500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>227400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>259300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>430000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>179400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>236400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>241500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>425200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>198200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>247900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>255000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>421200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>183100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>270900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>234100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>396500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>187200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>221300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>224400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>370000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>181400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>135900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>190600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>338700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>83800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>144200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>122100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>219200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>76800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>136900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>116800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>207300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>71400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>114600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>91900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>160600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>60300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>123600</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>89400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3148,8 +3206,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3234,17 +3295,17 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3252,12 +3313,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-4900</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3270,8 +3331,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3392,8 +3456,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3514,8 +3581,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3558,8 +3628,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3613,11 +3683,11 @@
         <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
@@ -3636,130 +3706,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>360700</v>
+      </c>
+      <c r="E33" s="3">
         <v>164500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>227400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>259300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>430000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>179400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>236400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>241500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>425200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>198200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>247900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>255000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>421200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>183100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>270900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>234100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>396500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>187200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>221300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>224400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>370000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>181400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>135900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>190600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>338700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>83800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>144200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>122100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>219200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>76800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>136900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>116800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>207300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>71400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>109700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>91900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>160600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>60300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>123600</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>89400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3880,257 +3956,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>360700</v>
+      </c>
+      <c r="E35" s="3">
         <v>164500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>227400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>259300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>430000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>179400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>236400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>241500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>425200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>198200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>247900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>255000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>421200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>183100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>270900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>234100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>396500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>187200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>221300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>224400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>370000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>181400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>135900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>190600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>338700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>83800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>144200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>122100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>219200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>76800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>136900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>116800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>207300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>71400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>109700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>91900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>160600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>60300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>123600</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>89400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E38" s="2">
         <v>46109</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46018</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45654</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45290</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44828</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44737</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44464</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44282</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44191</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4173,8 +4258,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4217,130 +4303,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>231600</v>
+      </c>
+      <c r="E41" s="3">
         <v>224300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>194100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>184600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>225800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>231700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>251500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>186300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>394700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>264100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>397100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>421700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>620000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>190100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>202500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>211200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>530800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>405400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>878000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1111700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1412000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1149900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1341800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1112000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1206400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>461500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>84200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>82600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>104000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>102200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>86300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>71300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>70000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>132400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>109100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>70000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>67800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>72700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>53900</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>55500</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4461,83 +4551,86 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>206000</v>
+      </c>
+      <c r="E43" s="3">
         <v>11300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27000</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>21600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>14400</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="3">
         <v>2500</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q43" s="3">
         <v>2600</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>8400</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>9000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>17100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA43" s="3">
         <v>7800</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
-      </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
@@ -4545,25 +4638,25 @@
         <v>0</v>
       </c>
       <c r="AD43" s="3">
-        <v>5600</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="3">
         <v>5600</v>
       </c>
       <c r="AF43" s="3">
+        <v>5600</v>
+      </c>
+      <c r="AG43" s="3">
         <v>4800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>23700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5100</v>
-      </c>
-      <c r="AJ43" s="3">
-        <v>4800</v>
       </c>
       <c r="AK43" s="3">
         <v>4800</v>
@@ -4572,141 +4665,147 @@
         <v>4800</v>
       </c>
       <c r="AM43" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AN43" s="3">
         <v>4100</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>7300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>3700</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>16300</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3518500</v>
+      </c>
+      <c r="E44" s="3">
         <v>3583600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3084100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3252800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3090300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3213900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2840200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3082500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3000000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3048700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2645900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2834200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2660100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3030700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2709600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2678200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2485100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2568200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2191200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2199800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1992800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2084700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1783300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1915000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1688500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1905900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1602800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1812800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1733200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1881300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1589500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1737300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1632300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1760100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1453200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1591600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1468300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1657800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1369700</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1489900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4749,208 +4848,214 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>245700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>211900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>214400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>185600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>164100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>149600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>162300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>146200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>133700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>136100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>135200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>112900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>100900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>104500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>95100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>90700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>114400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>109500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>103400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>86800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>88300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>75600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>90400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>86500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>90600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>68000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4254500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4041600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3507800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3647100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3543800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3656100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3309900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3483200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3639600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3519500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3263900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3534100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3577300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3458900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3157800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3109800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3230400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3168300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3250400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3467900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3567100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3380800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3258700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3171000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3030100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2480200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1787900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2005500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1937800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2079100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1794400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1941700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1810700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1984100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1655400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1742000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1630500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1824300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1517800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1629800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4993,8 +5098,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5071,150 +5176,156 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7334700</v>
+      </c>
+      <c r="E48" s="3">
         <v>7164000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6965000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6761300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6540400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6255000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6142900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5928600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5791900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5685900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5579200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5358600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5143300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5095400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5037400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4647100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4504700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4399800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4403700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4167200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4008900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3876400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3672800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3532800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3416800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3371800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3352800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3276300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3226700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3207800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1134500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1112000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1081500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1050400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1044500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>996800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>982400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>957000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>962300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>923200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>506200</v>
+      </c>
+      <c r="E49" s="3">
         <v>398200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>398800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>399300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>399600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>400700</v>
-      </c>
-      <c r="I49" s="3">
-        <v>269500</v>
       </c>
       <c r="J49" s="3">
         <v>269500</v>
@@ -5229,19 +5340,19 @@
         <v>269500</v>
       </c>
       <c r="N49" s="3">
+        <v>269500</v>
+      </c>
+      <c r="O49" s="3">
         <v>267300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>267100</v>
-      </c>
-      <c r="P49" s="3">
-        <v>253300</v>
       </c>
       <c r="Q49" s="3">
         <v>253300</v>
       </c>
       <c r="R49" s="3">
-        <v>55500</v>
+        <v>253300</v>
       </c>
       <c r="S49" s="3">
         <v>55500</v>
@@ -5265,7 +5376,7 @@
         <v>55500</v>
       </c>
       <c r="Z49" s="3">
-        <v>124500</v>
+        <v>55500</v>
       </c>
       <c r="AA49" s="3">
         <v>124500</v>
@@ -5304,7 +5415,7 @@
         <v>124500</v>
       </c>
       <c r="AM49" s="3">
-        <v>125700</v>
+        <v>124500</v>
       </c>
       <c r="AN49" s="3">
         <v>125700</v>
@@ -5313,10 +5424,13 @@
         <v>125700</v>
       </c>
       <c r="AP49" s="3">
+        <v>125700</v>
+      </c>
+      <c r="AQ49" s="3">
         <v>10300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5437,8 +5551,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5559,130 +5676,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E52" s="3">
         <v>58300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>62200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>68900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>75000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>73600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>83200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>86600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>83500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>80000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>75500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>45000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>45200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>41300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>41500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>99300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>78600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>63200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>57800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>54600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>56300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>46900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>62100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>32500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>39600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>25900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>24100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>23000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>23700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>25800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>31900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>42700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>50600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>48800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>44400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>65000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>77000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>69400</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>69100</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>72600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5803,130 +5926,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12161800</v>
+      </c>
+      <c r="E54" s="3">
         <v>11662100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10933700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10876600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10558800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10385300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9805500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9767900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9784500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9555000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9188200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9205000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9032800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8848800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8490000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>7911700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7869200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7686800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>7767500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>7745200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7687900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7359700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7049100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6860800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6611100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6002400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5289300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5429300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5312700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5437200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>3085300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3220900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3067400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3207800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2868800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2928400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2815600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2976400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2674900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2635700</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5969,8 +6098,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6013,740 +6143,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1760300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1760400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1390800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1549200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1519100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1559200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1236200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1349800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1436500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1515700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1179800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1412200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1272200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1526500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1398300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1219600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1280500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1341600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1155600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1197800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1221900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1181900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>976100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1056900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1003700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>887900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>643000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>679800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>681500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>785100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>620000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>683700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>649700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>732500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>576600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>609900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>510800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>563500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>519500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>484000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>473900</v>
+      </c>
+      <c r="E58" s="3">
         <v>462300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>455300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>421400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>413700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>406400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>391000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>385500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>380200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>372800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>368500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>320600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>316600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>384400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>384300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>34200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>34000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>33900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>26200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>24900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>29900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>30000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>28700</v>
-      </c>
-      <c r="AJ58" s="3">
-        <v>28500</v>
       </c>
       <c r="AK58" s="3">
         <v>28500</v>
       </c>
       <c r="AL58" s="3">
+        <v>28500</v>
+      </c>
+      <c r="AM58" s="3">
         <v>26000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>23400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>13900</v>
-      </c>
-      <c r="AO58" s="3">
-        <v>11300</v>
       </c>
       <c r="AP58" s="3">
         <v>11300</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>11300</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
         <v>12000</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>40900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>143300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>29600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>94900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="N59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O59" s="3">
         <v>33600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>114200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>974700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>872500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>958200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>854000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>905300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>844000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>856800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>789300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>763100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>691300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>769000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>572000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>570500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>538000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>563600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>501900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>288200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>260900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>263100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>252900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>244100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>236300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>272300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>239700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>246400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>217000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3189700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2929700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2614400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2802300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2762700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2600500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2319200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2345700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2544500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2517800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2177100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2318800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2237500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2349700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2376200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2095200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2242200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2199700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2064800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2046000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2083500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1975900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1743800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2132700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2157100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1494100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1247600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1251700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1271400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1311900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>938100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>974500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>941500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1013900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>849200</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>872200</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>806500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>817100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>777200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>712300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6071100</v>
+      </c>
+      <c r="E61" s="3">
         <v>5946500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5487600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5300900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5143700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5355300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5024200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4942700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4741000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4704200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4663200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4608800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4523400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4387200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1198700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1113400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1023300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1023500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1019200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1015900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1016000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1016700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1017400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>562200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>568100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1020200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>396900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>643100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>493700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>634000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>410400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>577200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>547000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>711300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>433700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>520700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>467500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>624400</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>289800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>310000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>169300</v>
+      </c>
+      <c r="E62" s="3">
         <v>158800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>155300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>147000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>142300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>149300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>147400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>141900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>139200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>140500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>138100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>136300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>125700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>121000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2872700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2762000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2689900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2673600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2680700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2662500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2608200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2514700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2364100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2290100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2190100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2134300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2077700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2042700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2002700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2005700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>175000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>173900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>172800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>169300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>167200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>164000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>159000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>155400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>154800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>148700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6867,8 +7016,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6989,8 +7141,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7111,130 +7266,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9530300</v>
+      </c>
+      <c r="E66" s="3">
         <v>9148300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8352400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8303400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8068500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8146800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7535200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7479100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7479200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7430900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7038400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7093900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6945700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6934300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6447600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5970600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5955300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5896800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5764800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5724400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5707800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5507400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5125300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4984900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4915300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>4648700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3722100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3937500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3767800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3951600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1523400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1725600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1661400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1894500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1450100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1557000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1433000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1596900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1221700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1171000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7277,8 +7438,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7399,8 +7561,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7521,8 +7686,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7643,8 +7811,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7765,130 +7936,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7792300</v>
+      </c>
+      <c r="E72" s="3">
         <v>7557300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7519100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7413100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7275700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6967700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6910700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6791600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6668000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6361300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6282000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6145500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6002500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5694000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5624400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5455100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5322900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5029000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4945200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4783100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4618000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4307900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4187100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4097900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>3953800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3655800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3612800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3510100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3429500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3252400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3213900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3115000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3036000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2866500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2829200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2753300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2695600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2569500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2540400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2448300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8009,8 +8186,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8131,8 +8311,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8253,130 +8436,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2631600</v>
+      </c>
+      <c r="E76" s="3">
         <v>2513700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2581300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2573200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2490300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2238500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2270300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2288800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2305300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2124000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2149800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2111100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2087200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1914500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2042400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1941100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1913900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1790000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2002700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2020800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1980100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1852300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1923800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1875900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1695700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1353700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1567100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1491800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1544900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1485600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1561800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1495300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1406000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1313200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1418700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1371400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1382600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1379500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1453200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1464700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8497,257 +8686,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46200</v>
+      </c>
+      <c r="E80" s="2">
         <v>46109</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46018</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45654</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45290</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44828</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44737</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44464</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44282</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44191</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42637</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>360700</v>
+      </c>
+      <c r="E81" s="3">
         <v>164500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>227400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>259300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>430000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>179400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>236400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>241500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>425200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>198200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>247900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>255000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>421200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>183100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>270900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>234100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>396500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>187200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>221300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>224400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>370000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>181400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>135900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>190600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>338700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>83800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>144200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>122100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>219200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>76800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>136900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>116800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>207300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>71400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>109700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>91900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>160600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>60300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>123600</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>89400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8790,130 +8988,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>120100</v>
+        <v>122100</v>
       </c>
       <c r="E83" s="3">
         <v>120100</v>
       </c>
       <c r="F83" s="3">
+        <v>120100</v>
+      </c>
+      <c r="G83" s="3">
         <v>113500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>109300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>104300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>103300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>90300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>102300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>97200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>94800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>87200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>83400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>77600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>94800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>87200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>83400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>77600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>75400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>69800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>64900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>60100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>58500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>54700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>52500</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>51400</v>
       </c>
       <c r="AC83" s="3">
         <v>51400</v>
       </c>
       <c r="AD83" s="3">
+        <v>51400</v>
+      </c>
+      <c r="AE83" s="3">
         <v>49800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>49000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>45800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>46000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>45000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>43600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>42800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>43100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>41900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>41000</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>39700</v>
       </c>
       <c r="AO83" s="3">
         <v>39700</v>
       </c>
       <c r="AP83" s="3">
+        <v>39700</v>
+      </c>
+      <c r="AQ83" s="3">
         <v>35700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9034,8 +9236,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9156,8 +9361,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9278,8 +9486,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9400,8 +9611,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9522,130 +9736,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>562000</v>
+      </c>
+      <c r="E89" s="3">
         <v>91100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>324800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>307900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>785800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>216800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>517200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>86300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>559900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>257400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>396100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>155600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>762800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>730600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>566500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>59100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>266900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>62900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>631800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>177100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>389500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>909200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>83900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>397400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>65500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>361900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-13000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>341000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>79400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>295900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-21900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>290500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>113500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>369200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-141700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>376700</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9688,130 +9908,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-233100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-202600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-265600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-277600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-210400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-141300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-246000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-188200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-192600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-157200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-227200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-177100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-191600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-157900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-322200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-185800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-152900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-112400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-246100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-166300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-115300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-132700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-74700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-57000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-73100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-60800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-54800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-28800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-84800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-77000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-71600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-45100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-98400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-55400</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-61700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-284900</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-66200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9932,8 +10156,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10054,130 +10281,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-324300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-171300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-101700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-228200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-187600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-261100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-183800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-128800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-179100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-152300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-198500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-110100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-186800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-157700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-642700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-185900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-152800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-112300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-246100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-165600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-115200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-100500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-132000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-74200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-56700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-29300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-72900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-59100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-54500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-28400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-84700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-75300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-71300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-45100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-96800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-51000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-34900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-202500</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-65900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10220,130 +10453,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>125600</v>
+      </c>
+      <c r="E96" s="3">
         <v>126400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>121400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>121900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>122000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>122400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>117300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>117800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>118500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>118800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>111400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>112000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>112800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>113400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-101700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-101900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-102600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-103500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-59200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-59400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-59900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-60600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-46600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-46500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-40600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-40800</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-41500</v>
       </c>
       <c r="AD96" s="3">
         <v>-41500</v>
       </c>
       <c r="AE96" s="3">
+        <v>-41500</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-42100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-37900</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-37800</v>
       </c>
       <c r="AI96" s="3">
         <v>-37800</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-33600</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-33900</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-34100</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-34600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-31300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-31400</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-32000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10464,8 +10701,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10586,8 +10826,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10708,130 +10951,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-230400</v>
+      </c>
+      <c r="E100" s="3">
         <v>110400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-213700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-120800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-604100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-268200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-165900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-250200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-238100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-222300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-243800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-146000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>125700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-96600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-134500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-288300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-419400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-254500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-197700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-254500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-268400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-27700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-107700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>322600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-322900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-27700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-305600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>57400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-241300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-287000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>90200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-154600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-55900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-323100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>195300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-164200</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-35800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10874,8 +11123,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10952,126 +11201,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E102" s="3">
         <v>30200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-41200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>65200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-208500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>130700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-133000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-24600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-198300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>430000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-319600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>125400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-472600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-233700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-300300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>262100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-191800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>229800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-94400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>744900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>377200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-21400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>15900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>15000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-62400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>23300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>39100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>2300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-4900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>18800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-95600</v>
       </c>
     </row>
